--- a/diseases/d169/2020-2025.xlsx
+++ b/diseases/d169/2020-2025.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1209,9 +1206,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1653,9 +1647,6 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.001928324877773368</v>
       </c>
@@ -2097,9 +2088,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2541,9 +2529,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2985,9 +2970,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3429,9 +3411,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -3873,9 +3852,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4317,9 +4293,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -4761,9 +4734,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5205,9 +5175,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -5649,9 +5616,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6093,9 +6057,6 @@
       <c r="O38" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.001928699917871136</v>
       </c>
@@ -6537,9 +6498,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -6981,9 +6939,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -7425,9 +7380,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -7869,9 +7821,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8313,9 +8262,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8757,9 +8703,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9201,9 +9144,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9645,9 +9585,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -10089,9 +10026,6 @@
       <c r="O65" t="n">
         <v>5</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.009643499589355679</v>
       </c>
@@ -10533,9 +10467,6 @@
       <c r="O68" t="n">
         <v>3</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.005786099753613407</v>
       </c>
@@ -10977,9 +10908,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11421,9 +11349,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -11717,9 +11642,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -12013,9 +11935,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -12457,9 +12376,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -12901,9 +12817,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -13345,9 +13258,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -13789,9 +13699,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -14233,9 +14140,6 @@
       <c r="O93" t="n">
         <v>1</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.001931153918635252</v>
       </c>
@@ -14529,9 +14433,6 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.001931153918635252</v>
       </c>
@@ -14973,9 +14874,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15417,9 +15315,6 @@
       <c r="O101" t="n">
         <v>1</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.001931153918635252</v>
       </c>
@@ -15861,9 +15756,6 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.001931153918635252</v>
       </c>
@@ -16157,9 +16049,6 @@
       <c r="O106" t="n">
         <v>1</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.001932414237185567</v>
       </c>
@@ -16601,9 +16490,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17045,9 +16931,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -17341,9 +17224,6 @@
       <c r="O114" t="n">
         <v>2</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.003864828474371134</v>
       </c>
@@ -17637,9 +17517,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -18081,9 +17958,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.001932414237185567</v>
       </c>
@@ -18525,9 +18399,6 @@
       <c r="O122" t="n">
         <v>1</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.001932414237185567</v>
       </c>
@@ -18969,9 +18840,6 @@
       <c r="O125" t="n">
         <v>5</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.009662071185927835</v>
       </c>
@@ -19413,9 +19281,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -19857,9 +19722,6 @@
       <c r="O131" t="n">
         <v>2</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.003864828474371134</v>
       </c>
@@ -20301,9 +20163,6 @@
       <c r="O134" t="n">
         <v>6</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.0115944854231134</v>
       </c>
@@ -20597,9 +20456,6 @@
       <c r="O136" t="n">
         <v>3</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.005797242711556701</v>
       </c>
@@ -21041,9 +20897,6 @@
       <c r="O139" t="n">
         <v>1</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.00193357811143172</v>
       </c>
@@ -21485,9 +21338,6 @@
       <c r="O142" t="n">
         <v>1</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.00193357811143172</v>
       </c>
@@ -21929,9 +21779,6 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.00193357811143172</v>
       </c>
@@ -22373,9 +22220,6 @@
       <c r="O148" t="n">
         <v>6</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.01160146866859032</v>
       </c>
@@ -22817,9 +22661,6 @@
       <c r="O151" t="n">
         <v>2</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.00386715622286344</v>
       </c>
@@ -23261,9 +23102,6 @@
       <c r="O154" t="n">
         <v>1</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.00193357811143172</v>
       </c>
@@ -23705,9 +23543,6 @@
       <c r="O157" t="n">
         <v>8</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.01546862489145376</v>
       </c>
@@ -24149,9 +23984,6 @@
       <c r="O160" t="n">
         <v>5</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.009667890557158599</v>
       </c>
@@ -24593,9 +24425,6 @@
       <c r="O163" t="n">
         <v>9</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.01740220300288548</v>
       </c>
@@ -24889,9 +24718,6 @@
       <c r="O165" t="n">
         <v>11</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.02126935922574892</v>
       </c>
@@ -25333,9 +25159,6 @@
       <c r="O168" t="n">
         <v>12</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.02320293733718064</v>
       </c>
@@ -25777,9 +25600,6 @@
       <c r="O171" t="n">
         <v>3</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.005800734334295159</v>
       </c>
@@ -26073,9 +25893,6 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.001935470278971621</v>
       </c>
@@ -26517,9 +26334,6 @@
       <c r="O176" t="n">
         <v>1</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.001935470278971621</v>
       </c>
@@ -26813,9 +26627,6 @@
       <c r="O178" t="n">
         <v>2</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.003870940557943243</v>
       </c>
@@ -27109,9 +26920,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -27553,9 +27361,6 @@
       <c r="O183" t="n">
         <v>5</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.009677351394858107</v>
       </c>
@@ -27997,9 +27802,6 @@
       <c r="O186" t="n">
         <v>1</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.001935470278971621</v>
       </c>
@@ -28441,9 +28243,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -28737,9 +28536,6 @@
       <c r="O191" t="n">
         <v>3</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.005806410836914865</v>
       </c>
@@ -29033,9 +28829,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -29329,9 +29122,6 @@
       <c r="O195" t="n">
         <v>1</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.001935470278971621</v>
       </c>
@@ -29625,9 +29415,6 @@
       <c r="O197" t="n">
         <v>2</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.003870940557943243</v>
       </c>
@@ -29919,9 +29706,6 @@
         <v>0</v>
       </c>
       <c r="O199" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q199" t="n">
         <v>0</v>
       </c>
       <c r="R199" t="n">
